--- a/UTCUTS/B1_Scenario_Config_REF.xlsx
+++ b/UTCUTS/B1_Scenario_Config_REF.xlsx
@@ -50954,5 +50954,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A356233F-3A5F-455E-B22F-9BA374C82A67}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F08C597-B0A6-4B95-8FE6-622AAB50C064}"/>
 </file>